--- a/recov.xlsx
+++ b/recov.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>irms.com.pk</t>
   </si>
@@ -117,9 +117,6 @@
     <t>cfapl.com</t>
   </si>
   <si>
-    <t>+92-21-34388431</t>
-  </si>
-  <si>
     <t xml:space="preserve">Central Facilitation Agency </t>
   </si>
   <si>
@@ -142,9 +139,6 @@
   </si>
   <si>
     <t>https://icilpk.com/</t>
-  </si>
-  <si>
-    <t>+92 2135246551-58</t>
   </si>
   <si>
     <t>info@icilpk.com</t>
@@ -180,12 +174,30 @@
   <si>
     <t xml:space="preserve"> </t>
   </si>
+  <si>
+    <t>+92-21-34388431 ye to K electric ka office he ap kal 11 bajy call krAIN</t>
+  </si>
+  <si>
+    <t>+92 21 3524 6551-58 dr</t>
+  </si>
+  <si>
+    <t> 0800-76933</t>
+  </si>
+  <si>
+    <t>Rozee com</t>
+  </si>
+  <si>
+    <t>rozee.com.pk</t>
+  </si>
+  <si>
+    <t>shahrai-faisal karachi</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -216,6 +228,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -258,7 +276,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -267,6 +285,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -548,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="21.140625" defaultRowHeight="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.85546875" customWidth="1"/>
@@ -582,16 +602,16 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" t="s">
         <v>38</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" t="s">
-        <v>40</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
@@ -602,7 +622,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
@@ -648,7 +668,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -662,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>45</v>
-      </c>
       <c r="F6" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -687,30 +707,44 @@
     </row>
     <row r="8" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
         <v>33</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>34</v>
       </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
